--- a/src/reg_map/register_map.xlsx
+++ b/src/reg_map/register_map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\Kerbal_Flight_Controller\src\reg_map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECF2802-58EE-47C6-92EA-07DBEC6647B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AF5216-F63A-4413-A6D7-F68B2F530DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller_caracteristic" sheetId="2" r:id="rId1"/>
@@ -21,12 +21,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="64">
   <si>
     <t>register_name</t>
   </si>
@@ -191,6 +194,33 @@
   </si>
   <si>
     <t>X"008C"</t>
+  </si>
+  <si>
+    <t>X"0014"</t>
+  </si>
+  <si>
+    <t>X"0018"</t>
+  </si>
+  <si>
+    <t>X"001C"</t>
+  </si>
+  <si>
+    <t>PVLT</t>
+  </si>
+  <si>
+    <t>Telemetry : Angular Velocity Pitch</t>
+  </si>
+  <si>
+    <t>RVLT</t>
+  </si>
+  <si>
+    <t>Telemetry : Angular Velocity Roll</t>
+  </si>
+  <si>
+    <t>YVLT</t>
+  </si>
+  <si>
+    <t>Telemetry : Angular Velocity Yaw</t>
   </si>
 </sst>
 </file>
@@ -509,13 +539,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7FDEFAA-62EE-41D2-A142-AA66F27CBE8F}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -523,7 +553,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -531,7 +561,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -539,7 +569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -547,7 +577,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -555,7 +585,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -563,7 +593,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -571,7 +601,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -579,7 +609,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -594,20 +624,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" customWidth="1"/>
-    <col min="2" max="2" width="17.109375" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="8" width="25.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="8" width="25.7109375" customWidth="1"/>
     <col min="9" max="9" width="134" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -636,7 +666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -665,7 +695,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -694,7 +724,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -723,7 +753,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -752,7 +782,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -781,102 +811,102 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7">
+        <v>31</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8">
+        <v>31</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9">
+        <v>31</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>43</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B10" t="s">
         <v>44</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C10" t="s">
         <v>43</v>
-      </c>
-      <c r="D7">
-        <v>31</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8">
-        <v>31</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9">
-        <v>31</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" t="s">
-        <v>52</v>
       </c>
       <c r="D10">
         <v>31</v>
@@ -894,6 +924,93 @@
         <v>31</v>
       </c>
       <c r="I10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11">
+        <v>31</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12">
+        <v>31</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13">
+        <v>31</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" t="s">
         <v>50</v>
       </c>
     </row>
